--- a/Result/profitability/2344.xlsx
+++ b/Result/profitability/2344.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.48</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3124999999999999</v>
+        <v>0.9875</v>
       </c>
       <c r="N2" t="n">
-        <v>30.3625</v>
+        <v>34.98</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.35</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2687499999999999</v>
+        <v>0.9625</v>
       </c>
       <c r="N3" t="n">
-        <v>27.095</v>
+        <v>31.97875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.24</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2575</v>
+        <v>0.9624999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>24.3825</v>
+        <v>29.46125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.9399999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>0.17</v>
+        <v>0.88125</v>
       </c>
       <c r="N5" t="n">
-        <v>18.2975</v>
+        <v>23.74625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-1.43</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02749999999999997</v>
+        <v>0.6212500000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>10.64625</v>
+        <v>13.09125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.76</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.14875</v>
+        <v>0.43125</v>
       </c>
       <c r="N7" t="n">
-        <v>3.161250000000001</v>
+        <v>6.210000000000001</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.27</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2775000000000001</v>
+        <v>0.11625</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8487499999999994</v>
+        <v>0.7612500000000009</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1648,7 +1648,7 @@
         <v>-0.4737500000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.584999999999999</v>
+        <v>-1.585</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1902,7 +1902,7 @@
         <v>-0.2925000000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>4.467500000000001</v>
+        <v>4.4675</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
         <v>-0.1737500000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>9.516250000000001</v>
+        <v>9.516249999999999</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>59843</v>
+      </c>
+      <c r="D75" t="n">
+        <v>20198</v>
+      </c>
+      <c r="E75" t="n">
+        <v>39645</v>
+      </c>
+      <c r="F75" t="n">
+        <v>66.25</v>
+      </c>
+      <c r="G75" t="n">
+        <v>28979</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>48.43%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1039</v>
+      </c>
+      <c r="J75" t="n">
+        <v>30018</v>
+      </c>
+      <c r="K75" t="n">
+        <v>24317</v>
+      </c>
+      <c r="L75" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.0475</v>
+      </c>
+      <c r="N75" t="n">
+        <v>39.1175</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>12.88</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.2413340828180626</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-19.62068965517242</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>43.59</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>1.923654015887025</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
